--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0003T0006Z000C1N38_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0003T0006Z000C1N38_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>85.76070343510419</v>
+        <v>13.93611430820443</v>
       </c>
       <c r="D2" t="n">
-        <v>76.63178468677739</v>
+        <v>12.45266501160133</v>
       </c>
       <c r="E2" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F2" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>75.31591722684283</v>
+        <v>12.23883654936196</v>
       </c>
       <c r="D3" t="n">
-        <v>71.03102572848994</v>
+        <v>11.54254168087962</v>
       </c>
       <c r="E3" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F3" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>98.88304077433534</v>
+        <v>16.06849412582949</v>
       </c>
       <c r="D4" t="n">
-        <v>96.30376930317668</v>
+        <v>15.64936251176621</v>
       </c>
       <c r="E4" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F4" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>59.51108381632031</v>
+        <v>9.67055112015205</v>
       </c>
       <c r="D5" t="n">
-        <v>54.41202889862439</v>
+        <v>8.841954696026464</v>
       </c>
       <c r="E5" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F5" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>54.59146666243687</v>
+        <v>8.871113332645992</v>
       </c>
       <c r="D6" t="n">
-        <v>50.06350080683198</v>
+        <v>8.135318881110198</v>
       </c>
       <c r="E6" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F6" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>56.53510183951349</v>
+        <v>9.186954048920942</v>
       </c>
       <c r="D7" t="n">
-        <v>54.68781044583223</v>
+        <v>8.886769197447737</v>
       </c>
       <c r="E7" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F7" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>48.43937563298327</v>
+        <v>7.871398540359782</v>
       </c>
       <c r="D8" t="n">
-        <v>45.01599431511134</v>
+        <v>7.315099076205593</v>
       </c>
       <c r="E8" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F8" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>56.46562121262372</v>
+        <v>9.175663447051356</v>
       </c>
       <c r="D9" t="n">
-        <v>56.08659998086137</v>
+        <v>9.114072496889973</v>
       </c>
       <c r="E9" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F9" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>25.89366880446185</v>
+        <v>4.207721180725051</v>
       </c>
       <c r="D10" t="n">
-        <v>26.04676491761714</v>
+        <v>4.232599299112786</v>
       </c>
       <c r="E10" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F10" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>34.88530444912026</v>
+        <v>5.668861972982043</v>
       </c>
       <c r="D11" t="n">
-        <v>35.1446733136234</v>
+        <v>5.711009413463803</v>
       </c>
       <c r="E11" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F11" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>58.88759399959122</v>
+        <v>9.569234024933575</v>
       </c>
       <c r="D12" t="n">
-        <v>58.58030439382293</v>
+        <v>9.519299463996227</v>
       </c>
       <c r="E12" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F12" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>9.056997961534412</v>
+        <v>1.471762168749342</v>
       </c>
       <c r="D13" t="n">
-        <v>10.82706812614317</v>
+        <v>1.759398570498265</v>
       </c>
       <c r="E13" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F13" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>17.13479008831204</v>
+        <v>2.784403389350707</v>
       </c>
       <c r="D14" t="n">
-        <v>17.16065873168169</v>
+        <v>2.788607043898275</v>
       </c>
       <c r="E14" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F14" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>14.63086564669608</v>
+        <v>2.377515667588114</v>
       </c>
       <c r="D15" t="n">
-        <v>11.72762995018456</v>
+        <v>1.905739866904992</v>
       </c>
       <c r="E15" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F15" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>19.98287560449219</v>
+        <v>3.247217285729981</v>
       </c>
       <c r="D16" t="n">
-        <v>18.74330968570149</v>
+        <v>3.045787823926492</v>
       </c>
       <c r="E16" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F16" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>33.81270338165513</v>
+        <v>5.494564299518959</v>
       </c>
       <c r="D17" t="n">
-        <v>37.47822642261592</v>
+        <v>6.090211793675087</v>
       </c>
       <c r="E17" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F17" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>18.60691072935547</v>
+        <v>3.023622993520264</v>
       </c>
       <c r="D18" t="n">
-        <v>18.46578867967735</v>
+        <v>3.000690660447569</v>
       </c>
       <c r="E18" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F18" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>72.8706484973912</v>
+        <v>11.84148038082607</v>
       </c>
       <c r="D19" t="n">
-        <v>30.38984695453372</v>
+        <v>4.93835013011173</v>
       </c>
       <c r="E19" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F19" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>86.66895917359574</v>
+        <v>14.08370586570931</v>
       </c>
       <c r="D20" t="n">
-        <v>27.50393264245895</v>
+        <v>4.469389054399579</v>
       </c>
       <c r="E20" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F20" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>30.22535083143761</v>
+        <v>4.911619510108612</v>
       </c>
       <c r="D21" t="n">
-        <v>34.83404576629262</v>
+        <v>5.66053243702255</v>
       </c>
       <c r="E21" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F21" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>24.88755333136911</v>
+        <v>4.044227416347481</v>
       </c>
       <c r="D22" t="n">
-        <v>24.73501776056092</v>
+        <v>4.01944038609115</v>
       </c>
       <c r="E22" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F22" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>48.25841556525025</v>
+        <v>7.841992529353165</v>
       </c>
       <c r="D23" t="n">
-        <v>52.69664033293938</v>
+        <v>8.56320405410265</v>
       </c>
       <c r="E23" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F23" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>58.43056156901697</v>
+        <v>9.494966254965258</v>
       </c>
       <c r="D24" t="n">
-        <v>46.83985623052769</v>
+        <v>7.61147663746075</v>
       </c>
       <c r="E24" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F24" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>71.86130783547389</v>
+        <v>11.67746252326451</v>
       </c>
       <c r="D25" t="n">
-        <v>29.91438118659782</v>
+        <v>4.861086942822146</v>
       </c>
       <c r="E25" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F25" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>51.02129217390846</v>
+        <v>8.290959978260124</v>
       </c>
       <c r="D26" t="n">
-        <v>50.87365822862063</v>
+        <v>8.266969462150854</v>
       </c>
       <c r="E26" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F26" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>69.55963740246381</v>
+        <v>11.30344107790037</v>
       </c>
       <c r="D27" t="n">
-        <v>54.72956433510355</v>
+        <v>8.893554204454327</v>
       </c>
       <c r="E27" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F27" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>103.3655383610105</v>
+        <v>16.7968999836642</v>
       </c>
       <c r="D28" t="n">
-        <v>8.10449975093441</v>
+        <v>1.316981209526842</v>
       </c>
       <c r="E28" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F28" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>94.00689668973425</v>
+        <v>15.27612071208182</v>
       </c>
       <c r="D29" t="n">
-        <v>8.786761685973335</v>
+        <v>1.427848773970667</v>
       </c>
       <c r="E29" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F29" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>62.49175003282135</v>
+        <v>10.15490938033347</v>
       </c>
       <c r="D30" t="n">
-        <v>62.35201040587486</v>
+        <v>10.13220169095467</v>
       </c>
       <c r="E30" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F30" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>49.63307229722037</v>
+        <v>8.06537424829831</v>
       </c>
       <c r="D31" t="n">
-        <v>49.47986912219167</v>
+        <v>8.040478732356146</v>
       </c>
       <c r="E31" t="n">
-        <v>25.84431146420415</v>
+        <v>4.199700612933175</v>
       </c>
       <c r="F31" t="n">
-        <v>21.34037185498874</v>
+        <v>3.46781042643567</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
